--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260612.xlsx
@@ -1019,17 +1019,17 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>精測</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>930,000</t>
+          <t>2,267,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1041,17 +1041,17 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>精測</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,267,000</t>
+          <t>930,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>中鋼</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>5,163,000</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>中鋼</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>5,163,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>1815</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>富喬</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>107,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>1815</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>富喬</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>107,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
